--- a/processed_data/hard_data_exports/hunt_tables/2026/2026_BLACK_BEAR.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/2026_BLACK_BEAR.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_BLACK_BEAR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026_BLACK_BEAR" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_BLACK_BEAR'!$A$3:$J$109</definedName>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -593,6 +593,26 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Harvest Success (Prior Year %)</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Average Harvest Age (Prior Year)</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Average Days Hunted (Prior Year)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1213,6 +1233,16 @@
       <c r="J17" s="7" t="n">
         <v>10</v>
       </c>
+      <c r="K17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1259,6 +1289,16 @@
       <c r="J18" s="5" t="n">
         <v>54</v>
       </c>
+      <c r="K18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -1305,6 +1345,16 @@
       <c r="J19" s="7" t="n">
         <v>19</v>
       </c>
+      <c r="K19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1351,6 +1401,16 @@
       <c r="J20" s="5" t="n">
         <v>18</v>
       </c>
+      <c r="K20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -1397,6 +1457,16 @@
       <c r="J21" s="7" t="n">
         <v>7</v>
       </c>
+      <c r="K21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22" ht="38" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1443,6 +1513,16 @@
       <c r="J22" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="K22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23" ht="38" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -1489,6 +1569,16 @@
       <c r="J23" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="K23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24" ht="38" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -1535,6 +1625,16 @@
       <c r="J24" s="5" t="n">
         <v>9</v>
       </c>
+      <c r="K24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25" ht="38" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -1581,6 +1681,16 @@
       <c r="J25" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="K25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26" ht="38" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -1627,6 +1737,16 @@
       <c r="J26" s="5" t="n">
         <v>22</v>
       </c>
+      <c r="K26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27" ht="38" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
@@ -1673,6 +1793,16 @@
       <c r="J27" s="7" t="n">
         <v>7</v>
       </c>
+      <c r="K27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28" ht="38" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -1719,6 +1849,16 @@
       <c r="J28" s="5" t="n">
         <v>38</v>
       </c>
+      <c r="K28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29" ht="38" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -1765,6 +1905,16 @@
       <c r="J29" s="7" t="n">
         <v>7</v>
       </c>
+      <c r="K29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30" ht="38" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -1811,6 +1961,16 @@
       <c r="J30" s="5" t="n">
         <v>40</v>
       </c>
+      <c r="K30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31" ht="38" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -1857,6 +2017,16 @@
       <c r="J31" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="K31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32" ht="38" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -1903,6 +2073,16 @@
       <c r="J32" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="K32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33" ht="38" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -1949,6 +2129,16 @@
       <c r="J33" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="K33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34" ht="38" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -2087,6 +2277,16 @@
       <c r="J36" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="K36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37" ht="38" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -2133,6 +2333,16 @@
       <c r="J37" s="7" t="n">
         <v>15</v>
       </c>
+      <c r="K37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38" ht="38" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -2179,6 +2389,16 @@
       <c r="J38" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="K38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39" ht="38" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
@@ -2225,6 +2445,16 @@
       <c r="J39" s="7" t="n">
         <v>18</v>
       </c>
+      <c r="K39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40" ht="38" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -2271,6 +2501,16 @@
       <c r="J40" s="5" t="n">
         <v>20</v>
       </c>
+      <c r="K40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41" ht="38" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
@@ -2317,6 +2557,16 @@
       <c r="J41" s="7" t="n">
         <v>8</v>
       </c>
+      <c r="K41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42" ht="38" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -2363,6 +2613,16 @@
       <c r="J42" s="5" t="n">
         <v>3</v>
       </c>
+      <c r="K42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43" ht="38" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
@@ -2409,6 +2669,16 @@
       <c r="J43" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="K43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44" ht="38" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -2455,6 +2725,16 @@
       <c r="J44" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="K44" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45" ht="38" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
@@ -2501,6 +2781,16 @@
       <c r="J45" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="K45" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46" ht="38" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -2547,6 +2837,16 @@
       <c r="J46" s="5" t="n">
         <v>3</v>
       </c>
+      <c r="K46" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47" ht="38" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
@@ -2593,6 +2893,16 @@
       <c r="J47" s="7" t="n">
         <v>14</v>
       </c>
+      <c r="K47" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48" ht="38" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -2639,6 +2949,16 @@
       <c r="J48" s="5" t="n">
         <v>7</v>
       </c>
+      <c r="K48" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49" ht="38" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
@@ -2685,6 +3005,16 @@
       <c r="J49" s="7" t="n">
         <v>24</v>
       </c>
+      <c r="K49" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50" ht="38" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -2731,6 +3061,16 @@
       <c r="J50" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="K50" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51" ht="38" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
@@ -2777,6 +3117,16 @@
       <c r="J51" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="K51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52" ht="38" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -2823,6 +3173,16 @@
       <c r="J52" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="K52" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53" ht="38" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
@@ -2869,6 +3229,16 @@
       <c r="J53" s="7" t="n">
         <v>23</v>
       </c>
+      <c r="K53" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54" ht="38" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -2915,6 +3285,16 @@
       <c r="J54" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="K54" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55" ht="38" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
@@ -2961,6 +3341,16 @@
       <c r="J55" s="7" t="n">
         <v>7</v>
       </c>
+      <c r="K55" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56" ht="38" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -3007,6 +3397,16 @@
       <c r="J56" s="5" t="n">
         <v>6</v>
       </c>
+      <c r="K56" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57" ht="38" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
@@ -3053,6 +3453,16 @@
       <c r="J57" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="K57" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58" ht="38" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -3099,6 +3509,16 @@
       <c r="J58" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="K58" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59" ht="38" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
@@ -3237,6 +3657,16 @@
       <c r="J61" s="7" t="n">
         <v>10</v>
       </c>
+      <c r="K61" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62" ht="38" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -3283,6 +3713,16 @@
       <c r="J62" s="5" t="n">
         <v>20</v>
       </c>
+      <c r="K62" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63" ht="38" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
@@ -3329,6 +3769,16 @@
       <c r="J63" s="7" t="n">
         <v>11</v>
       </c>
+      <c r="K63" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64" ht="38" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -3375,6 +3825,16 @@
       <c r="J64" s="5" t="n">
         <v>20</v>
       </c>
+      <c r="K64" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65" ht="38" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
@@ -3421,6 +3881,16 @@
       <c r="J65" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="K65" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66" ht="38" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -3467,6 +3937,16 @@
       <c r="J66" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="K66" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67" ht="38" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -3513,6 +3993,16 @@
       <c r="J67" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="K67" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68" ht="38" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -3559,6 +4049,16 @@
       <c r="J68" s="5" t="n">
         <v>29</v>
       </c>
+      <c r="K68" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69" ht="38" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
@@ -3605,6 +4105,16 @@
       <c r="J69" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="K69" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70" ht="38" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
@@ -3651,6 +4161,16 @@
       <c r="J70" s="5" t="n">
         <v>9</v>
       </c>
+      <c r="K70" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71" ht="38" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -3697,6 +4217,16 @@
       <c r="J71" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="K71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72" ht="38" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -3743,6 +4273,16 @@
       <c r="J72" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="K72" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73" ht="38" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
@@ -3789,6 +4329,16 @@
       <c r="J73" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="K73" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74" ht="38" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -3835,6 +4385,16 @@
       <c r="J74" s="5" t="n">
         <v>6</v>
       </c>
+      <c r="K74" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75" ht="38" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
@@ -3881,6 +4441,16 @@
       <c r="J75" s="7" t="n">
         <v>7</v>
       </c>
+      <c r="K75" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76" ht="38" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
@@ -3927,6 +4497,16 @@
       <c r="J76" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="K76" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77" ht="38" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
@@ -3973,6 +4553,16 @@
       <c r="J77" s="7" t="n">
         <v>9</v>
       </c>
+      <c r="K77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78" ht="38" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -4019,6 +4609,16 @@
       <c r="J78" s="5" t="n">
         <v>20</v>
       </c>
+      <c r="K78" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79" ht="38" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
@@ -4065,6 +4665,16 @@
       <c r="J79" s="7" t="n">
         <v>15</v>
       </c>
+      <c r="K79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80" ht="38" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
@@ -4111,6 +4721,16 @@
       <c r="J80" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="K80" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81" ht="38" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4157,6 +4777,16 @@
       <c r="J81" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="K81" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82" ht="38" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -4203,6 +4833,16 @@
       <c r="J82" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="K82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83" ht="38" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -4387,6 +5027,16 @@
       <c r="J86" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="K86" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87" ht="38" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
@@ -4433,6 +5083,16 @@
       <c r="J87" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="K87" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88" ht="38" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -4479,6 +5139,16 @@
       <c r="J88" s="5" t="n">
         <v>14</v>
       </c>
+      <c r="K88" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89" ht="38" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
@@ -4525,6 +5195,16 @@
       <c r="J89" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="K89" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90" ht="38" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
@@ -4571,6 +5251,16 @@
       <c r="J90" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="K90" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91" ht="38" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
@@ -4613,6 +5303,16 @@
       <c r="J91" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="K91" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92" ht="38" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -4659,6 +5359,16 @@
       <c r="J92" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="K92" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93" ht="38" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
@@ -4705,6 +5415,16 @@
       <c r="J93" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="K93" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94" ht="38" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
@@ -4751,6 +5471,16 @@
       <c r="J94" s="5" t="n">
         <v>11</v>
       </c>
+      <c r="K94" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95" ht="38" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
@@ -4797,6 +5527,16 @@
       <c r="J95" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="K95" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96" ht="38" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
@@ -4843,6 +5583,16 @@
       <c r="J96" s="5" t="n">
         <v>12</v>
       </c>
+      <c r="K96" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97" ht="38" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
@@ -4889,6 +5639,16 @@
       <c r="J97" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="K97" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98" ht="38" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
@@ -4935,6 +5695,16 @@
       <c r="J98" s="5" t="n">
         <v>3</v>
       </c>
+      <c r="K98" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99" ht="38" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -4981,6 +5751,16 @@
       <c r="J99" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="K99" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100" ht="38" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
@@ -5027,6 +5807,16 @@
       <c r="J100" s="5" t="n">
         <v>15</v>
       </c>
+      <c r="K100" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101" ht="38" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -5073,6 +5863,16 @@
       <c r="J101" s="7" t="n">
         <v>10</v>
       </c>
+      <c r="K101" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102" ht="38" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
@@ -5119,6 +5919,16 @@
       <c r="J102" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="K102" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103" ht="38" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
@@ -5165,6 +5975,16 @@
       <c r="J103" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="K103" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104" ht="38" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
@@ -5211,6 +6031,16 @@
       <c r="J104" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="K104" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105" ht="38" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
@@ -5257,6 +6087,16 @@
       <c r="J105" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="K105" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106" ht="38" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
@@ -5303,6 +6143,16 @@
       <c r="J106" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="K106" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107" ht="38" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
@@ -5343,6 +6193,16 @@
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
       <c r="J107" s="7" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108" ht="38" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
